--- a/Spec-20260801.xlsx
+++ b/Spec-20260801.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\專案\00_專案整理_20260501\個人網站_20260721\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FB28DE-3BA7-4056-BD6C-1AAB236584FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579BC32D-CE98-4DD9-86DF-66FDE88B4906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="blogs" sheetId="1" r:id="rId1"/>
+    <sheet name="Component" sheetId="2" r:id="rId2"/>
+    <sheet name="連結" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,8 +26,50 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="3">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="3">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Event</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,6 +88,62 @@
   </si>
   <si>
     <t>Learning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Navbar.jsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Header</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FeatureSection.jsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一邊是圖片一邊是文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TechMarquee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輪播內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ScrollingDataWall </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CertificationShowcase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.pexels.com/search/videos/business/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroCarousel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hero Banner</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -51,7 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,13 +166,27 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -84,14 +198,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -104,6 +228,80 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,4 +599,117 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7289D999-E12F-430D-90C4-E809DD8456CA}">
+  <dimension ref="B1:H15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="5" max="5" width="42.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="10" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="11" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="13" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="15" spans="2:8" ht="99.4" customHeight="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85414FBF-BF99-4C82-8DCF-C5271371050A}">
+  <dimension ref="C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="25.92578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{C9596D1B-AAED-407E-A0AB-B4C209CE406D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Spec-20260801.xlsx
+++ b/Spec-20260801.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\專案\00_專案整理_20260501\個人網站_20260721\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579BC32D-CE98-4DD9-86DF-66FDE88B4906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022C7275-756F-4D8A-B8FB-8394F7BCA187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="blogs" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
   <dimension ref="C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="25.92578125" customWidth="1"/>
+    <col min="3" max="3" width="57.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:3" x14ac:dyDescent="0.45">
